--- a/output/Tables/Best practice/cases_prev_target_area.xlsx
+++ b/output/Tables/Best practice/cases_prev_target_area.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>23097.45376066938</v>
+        <v>52292.88987005932</v>
       </c>
       <c r="D2">
-        <v>21917.06446397378</v>
+        <v>40267.21649479034</v>
       </c>
       <c r="E2">
-        <v>24339.53800611492</v>
+        <v>64457.56901727636</v>
       </c>
       <c r="F2">
-        <v>298521.5271842326</v>
+        <v>700183.6535500182</v>
       </c>
       <c r="G2">
-        <v>266122.2126181076</v>
+        <v>505624.7052847089</v>
       </c>
       <c r="H2">
-        <v>329454.2725148639</v>
+        <v>893458.098147049</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>39703363115.50294</v>
+        <v>93124425922.15242</v>
       </c>
       <c r="M2">
-        <v>35394254278.20831</v>
+        <v>67248085802.86628</v>
       </c>
       <c r="N2">
-        <v>43817418244.4769</v>
+        <v>118829927053.5575</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>19370.12329902716</v>
+        <v>41916.39684632578</v>
       </c>
       <c r="D3">
-        <v>19826.25779759773</v>
+        <v>35077.8679945683</v>
       </c>
       <c r="E3">
-        <v>19156.98907776078</v>
+        <v>49124.48106016488</v>
       </c>
       <c r="F3">
-        <v>242900.6353347943</v>
+        <v>541865.3030779496</v>
       </c>
       <c r="G3">
-        <v>235684.1781095685</v>
+        <v>427590.883842962</v>
       </c>
       <c r="H3">
-        <v>251450.3891341221</v>
+        <v>658577.2451518901</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>32305784499.52764</v>
+        <v>72068085309.36729</v>
       </c>
       <c r="M3">
-        <v>31345995688.57261</v>
+        <v>56869587551.11395</v>
       </c>
       <c r="N3">
-        <v>33442901754.83824</v>
+        <v>87590773605.20139</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>25363.65647208407</v>
+        <v>60632.75215350388</v>
       </c>
       <c r="D4">
-        <v>22396.77597872159</v>
+        <v>43210.87296639804</v>
       </c>
       <c r="E4">
-        <v>28179.89918589521</v>
+        <v>77837.05823172575</v>
       </c>
       <c r="F4">
-        <v>356593.1631501114</v>
+        <v>907792.5650244171</v>
       </c>
       <c r="G4">
-        <v>287714.6906993586</v>
+        <v>592759.7576164699</v>
       </c>
       <c r="H4">
-        <v>419811.331003999</v>
+        <v>1213381.78354892</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>47426890698.96482</v>
+        <v>120736411148.2475</v>
       </c>
       <c r="M4">
-        <v>38266053863.0147</v>
+        <v>78837047762.99049</v>
       </c>
       <c r="N4">
-        <v>55834907023.53188</v>
+        <v>161379777212.0064</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>11696.76815628306</v>
+        <v>79639.14226347416</v>
       </c>
       <c r="D5">
-        <v>7780.126950290891</v>
+        <v>60228.31205921528</v>
       </c>
       <c r="E5">
-        <v>16141.49420146841</v>
+        <v>99159.63273844472</v>
       </c>
       <c r="F5">
-        <v>12133.73789048171</v>
+        <v>81719.45139434267</v>
       </c>
       <c r="G5">
-        <v>6026.324169206112</v>
+        <v>46416.00403947769</v>
       </c>
       <c r="H5">
-        <v>20883.89291151867</v>
+        <v>126973.0843853021</v>
       </c>
       <c r="I5">
-        <v>651533379.8412814</v>
+        <v>4436059502.360087</v>
       </c>
       <c r="J5">
-        <v>433368631.3851057</v>
+        <v>3354837438.322411</v>
       </c>
       <c r="K5">
-        <v>899113510.0101956</v>
+        <v>5523389862.796827</v>
       </c>
       <c r="L5">
-        <v>1613787139.434067</v>
+        <v>10868687035.44757</v>
       </c>
       <c r="M5">
-        <v>801501114.5044129</v>
+        <v>6173328537.250532</v>
       </c>
       <c r="N5">
-        <v>2777557757.231983</v>
+        <v>16887420223.24518</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>9090.7557443195</v>
+        <v>63287.78248113526</v>
       </c>
       <c r="D6">
-        <v>6674.16140322043</v>
+        <v>52111.61602501425</v>
       </c>
       <c r="E6">
-        <v>11920.27196069442</v>
+        <v>74946.15772170122</v>
       </c>
       <c r="F6">
-        <v>9175.574388626885</v>
+        <v>63276.76337032349</v>
       </c>
       <c r="G6">
-        <v>5059.28097278613</v>
+        <v>39386.95153463051</v>
       </c>
       <c r="H6">
-        <v>15026.35384012389</v>
+        <v>93470.44800518264</v>
       </c>
       <c r="I6">
-        <v>506373276.4700844</v>
+        <v>3525256059.764159</v>
       </c>
       <c r="J6">
-        <v>371764138.4821846</v>
+        <v>2902721235.825336</v>
       </c>
       <c r="K6">
-        <v>663982988.7546004</v>
+        <v>4174650877.414178</v>
       </c>
       <c r="L6">
-        <v>1220351393.687376</v>
+        <v>8415809528.253024</v>
       </c>
       <c r="M6">
-        <v>672884369.3805554</v>
+        <v>5238464554.105858</v>
       </c>
       <c r="N6">
-        <v>1998505060.736477</v>
+        <v>12431569584.68929</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>13960.41305161223</v>
+        <v>92665.13976438958</v>
       </c>
       <c r="D7">
-        <v>8480.378690850332</v>
+        <v>64534.29602865379</v>
       </c>
       <c r="E7">
-        <v>19984.99505630456</v>
+        <v>120322.4693931323</v>
       </c>
       <c r="F7">
-        <v>15754.4253960954</v>
+        <v>102715.2150998541</v>
       </c>
       <c r="G7">
-        <v>7059.545718137066</v>
+        <v>52929.6769003886</v>
       </c>
       <c r="H7">
-        <v>28095.58211216867</v>
+        <v>166992.343900231</v>
       </c>
       <c r="I7">
-        <v>777622927.8009059</v>
+        <v>5161633615.155979</v>
       </c>
       <c r="J7">
-        <v>472374053.8377464</v>
+        <v>3594689357.388062</v>
       </c>
       <c r="K7">
-        <v>1113204194.626277</v>
+        <v>6702202190.136301</v>
       </c>
       <c r="L7">
-        <v>2095338577.680689</v>
+        <v>13661123608.28059</v>
       </c>
       <c r="M7">
-        <v>938919580.5122297</v>
+        <v>7039647027.751684</v>
       </c>
       <c r="N7">
-        <v>3736712420.918433</v>
+        <v>22209981738.73072</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>7807.969906813774</v>
+        <v>273837.4202767641</v>
       </c>
       <c r="D8">
-        <v>1701.767435041758</v>
+        <v>198414.3278513882</v>
       </c>
       <c r="E8">
-        <v>15748.83198109786</v>
+        <v>348820.2036360516</v>
       </c>
       <c r="F8">
-        <v>12488.97347109676</v>
+        <v>432043.4470685198</v>
       </c>
       <c r="G8">
-        <v>2153.534940707273</v>
+        <v>242241.4342008198</v>
       </c>
       <c r="H8">
-        <v>29087.72122855713</v>
+        <v>642663.4610034378</v>
       </c>
       <c r="I8">
-        <v>115612610.4101912</v>
+        <v>4054710682.038078</v>
       </c>
       <c r="J8">
-        <v>25198070.41066327</v>
+        <v>2937920952.495499</v>
       </c>
       <c r="K8">
-        <v>233192955.1441161</v>
+        <v>5164980755.238992</v>
       </c>
       <c r="L8">
-        <v>1661033471.655869</v>
+        <v>57461778460.11314</v>
       </c>
       <c r="M8">
-        <v>286420147.1140673</v>
+        <v>32218110748.70904</v>
       </c>
       <c r="N8">
-        <v>3868666923.398098</v>
+        <v>85474240313.45721</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>5725.28207245823</v>
+        <v>212525.446249702</v>
       </c>
       <c r="D9">
-        <v>1247.840181714227</v>
+        <v>167472.2715808359</v>
       </c>
       <c r="E9">
-        <v>11548.0088268336</v>
+        <v>258510.1611876505</v>
       </c>
       <c r="F9">
-        <v>9169.256039678527</v>
+        <v>334246.975272383</v>
       </c>
       <c r="G9">
-        <v>1581.099784336773</v>
+        <v>202682.5883860864</v>
       </c>
       <c r="H9">
-        <v>21355.85956465411</v>
+        <v>477023.5892493287</v>
       </c>
       <c r="I9">
-        <v>84774251.64688888</v>
+        <v>3146864282.619343</v>
       </c>
       <c r="J9">
-        <v>18476769.5706426</v>
+        <v>2479761925.29746</v>
       </c>
       <c r="K9">
-        <v>170991366.698925</v>
+        <v>3827759956.705527</v>
       </c>
       <c r="L9">
-        <v>1219511053.277244</v>
+        <v>44454847711.22694</v>
       </c>
       <c r="M9">
-        <v>210286271.3167908</v>
+        <v>26956784255.34949</v>
       </c>
       <c r="N9">
-        <v>2840329322.098996</v>
+        <v>63444137370.16071</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>11169.95247344146</v>
+        <v>356886.7559033735</v>
       </c>
       <c r="D10">
-        <v>2188.889113007589</v>
+        <v>233590.4753474353</v>
       </c>
       <c r="E10">
-        <v>22605.94089883021</v>
+        <v>476432.2218682657</v>
       </c>
       <c r="F10">
-        <v>19678.61126012159</v>
+        <v>613543.4162822388</v>
       </c>
       <c r="G10">
-        <v>2905.515884647718</v>
+        <v>309083.097915557</v>
       </c>
       <c r="H10">
-        <v>46052.9494353992</v>
+        <v>956568.5248718999</v>
       </c>
       <c r="I10">
-        <v>165393486.2742481</v>
+        <v>5284422194.661292</v>
       </c>
       <c r="J10">
-        <v>32410881.09630337</v>
+        <v>3458774168.469512</v>
       </c>
       <c r="K10">
-        <v>334726166.8889789</v>
+        <v>7054531909.203349</v>
       </c>
       <c r="L10">
-        <v>2617255297.596172</v>
+        <v>81601274365.53777</v>
       </c>
       <c r="M10">
-        <v>386433612.6581466</v>
+        <v>41108052022.76908</v>
       </c>
       <c r="N10">
-        <v>6125042274.908093</v>
+        <v>127223613807.9627</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1840.779170157067</v>
+        <v>29043.91197939255</v>
       </c>
       <c r="D11">
-        <v>-145.9688241586456</v>
+        <v>20726.06188015699</v>
       </c>
       <c r="E11">
-        <v>3709.840711931893</v>
+        <v>37285.2357976984</v>
       </c>
       <c r="F11">
-        <v>3670.977240118758</v>
+        <v>57597.60709435066</v>
       </c>
       <c r="G11">
-        <v>-216.6325326082901</v>
+        <v>30316.17848299707</v>
       </c>
       <c r="H11">
-        <v>9393.07244272732</v>
+        <v>94296.27530055412</v>
       </c>
       <c r="I11">
-        <v>138428434.3749808</v>
+        <v>2184131224.762307</v>
       </c>
       <c r="J11">
-        <v>-10977001.54555432</v>
+        <v>1558620579.449674</v>
       </c>
       <c r="K11">
-        <v>278983731.377991</v>
+        <v>2803887017.222727</v>
       </c>
       <c r="L11">
-        <v>488239972.9357948</v>
+        <v>7660481743.548637</v>
       </c>
       <c r="M11">
-        <v>-28812126.83690259</v>
+        <v>4032051738.23861</v>
       </c>
       <c r="N11">
-        <v>1249278634.882734</v>
+        <v>12541404614.9737</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>1330.50960973859</v>
+        <v>22287.45097384628</v>
       </c>
       <c r="D12">
-        <v>-105.5058240629434</v>
+        <v>17386.43125552672</v>
       </c>
       <c r="E12">
-        <v>2681.461632034695</v>
+        <v>27270.31327301613</v>
       </c>
       <c r="F12">
-        <v>2669.737638131259</v>
+        <v>44244.9059353421</v>
       </c>
       <c r="G12">
-        <v>-157.5471565520639</v>
+        <v>25279.45075175902</v>
       </c>
       <c r="H12">
-        <v>6831.16167651077</v>
+        <v>69362.18778621539</v>
       </c>
       <c r="I12">
-        <v>100055653.1619519</v>
+        <v>1676038600.68422</v>
       </c>
       <c r="J12">
-        <v>-7934143.475357383</v>
+        <v>1307477016.846878</v>
       </c>
       <c r="K12">
-        <v>201648596.1906414</v>
+        <v>2050754828.444095</v>
       </c>
       <c r="L12">
-        <v>355075105.8714574</v>
+        <v>5884572489.400498</v>
       </c>
       <c r="M12">
-        <v>-20953771.8214245</v>
+        <v>3362166949.98395</v>
       </c>
       <c r="N12">
-        <v>908544502.9759325</v>
+        <v>9225170975.566647</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>2711.792120236709</v>
+        <v>38800.83638920029</v>
       </c>
       <c r="D13">
-        <v>-200.8998360724534</v>
+        <v>24963.76886312597</v>
       </c>
       <c r="E13">
-        <v>5420.497659062895</v>
+        <v>52184.27735069978</v>
       </c>
       <c r="F13">
-        <v>5854.117316589164</v>
+        <v>82544.69636917207</v>
       </c>
       <c r="G13">
-        <v>-314.9795863069659</v>
+        <v>39037.47692295467</v>
       </c>
       <c r="H13">
-        <v>14814.53357193394</v>
+        <v>141627.6724947709</v>
       </c>
       <c r="I13">
-        <v>203929479.2339212</v>
+        <v>2917861697.304237</v>
       </c>
       <c r="J13">
-        <v>-15107868.57248455</v>
+        <v>1877300382.275927</v>
       </c>
       <c r="K13">
-        <v>407626844.4591895</v>
+        <v>3924309841.049982</v>
       </c>
       <c r="L13">
-        <v>778597603.1063589</v>
+        <v>10978444617.09989</v>
       </c>
       <c r="M13">
-        <v>-41892284.97882646</v>
+        <v>5191984430.752972</v>
       </c>
       <c r="N13">
-        <v>1970332965.067214</v>
+        <v>18836480441.80453</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>3156.213946770902</v>
+        <v>14446.94953747251</v>
       </c>
       <c r="D14">
-        <v>2609.004754778901</v>
+        <v>11495.33524266757</v>
       </c>
       <c r="E14">
-        <v>3682.289309750315</v>
+        <v>17471.75180789518</v>
       </c>
       <c r="F14">
-        <v>5907.255698169928</v>
+        <v>26504.44242258856</v>
       </c>
       <c r="G14">
-        <v>3711.411674080375</v>
+        <v>15984.74499090185</v>
       </c>
       <c r="H14">
-        <v>8109.696288986516</v>
+        <v>37699.27310719046</v>
       </c>
       <c r="I14">
-        <v>53147486.64967524</v>
+        <v>243272183.261501</v>
       </c>
       <c r="J14">
-        <v>43933031.06572188</v>
+        <v>193569950.1512797</v>
       </c>
       <c r="K14">
-        <v>62006069.68688547</v>
+        <v>294206828.6931463</v>
       </c>
       <c r="L14">
-        <v>785665007.8566004</v>
+        <v>3525090842.204278</v>
       </c>
       <c r="M14">
-        <v>493617752.6526899</v>
+        <v>2125971083.789947</v>
       </c>
       <c r="N14">
-        <v>1078589606.435207</v>
+        <v>5014003323.256331</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>2539.237373239866</v>
+        <v>11943.00822564268</v>
       </c>
       <c r="D15">
-        <v>2261.3441742655</v>
+        <v>10236.33235422225</v>
       </c>
       <c r="E15">
-        <v>2816.569780577678</v>
+        <v>13776.85963152902</v>
       </c>
       <c r="F15">
-        <v>4607.211774132114</v>
+        <v>21291.45792398265</v>
       </c>
       <c r="G15">
-        <v>3131.634754774218</v>
+        <v>13937.53281301116</v>
       </c>
       <c r="H15">
-        <v>6022.72107678557</v>
+        <v>28872.39850697506</v>
       </c>
       <c r="I15">
-        <v>42758218.12798602</v>
+        <v>201108315.511596</v>
       </c>
       <c r="J15">
-        <v>38078774.55045669</v>
+        <v>172369600.5127487</v>
       </c>
       <c r="K15">
-        <v>47428218.53514769</v>
+        <v>231988539.335317</v>
       </c>
       <c r="L15">
-        <v>612759165.9595711</v>
+        <v>2831763903.889693</v>
       </c>
       <c r="M15">
-        <v>416507422.384971</v>
+        <v>1853691864.130485</v>
       </c>
       <c r="N15">
-        <v>801021903.2124809</v>
+        <v>3840029001.427683</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>3648.474769842909</v>
+        <v>16313.52152677028</v>
       </c>
       <c r="D16">
-        <v>2845.192125985731</v>
+        <v>12202.21959089758</v>
       </c>
       <c r="E16">
-        <v>4409.690087088088</v>
+        <v>20431.31024465632</v>
       </c>
       <c r="F16">
-        <v>7246.102201780566</v>
+        <v>31466.66098866356</v>
       </c>
       <c r="G16">
-        <v>4229.47764730785</v>
+        <v>17453.23494520813</v>
       </c>
       <c r="H16">
-        <v>10358.15891274606</v>
+        <v>46692.18583311304</v>
       </c>
       <c r="I16">
-        <v>61436666.64938486</v>
+        <v>274703388.9892849</v>
       </c>
       <c r="J16">
-        <v>47910190.20947383</v>
+        <v>205473175.6911253</v>
       </c>
       <c r="K16">
-        <v>74254771.37647636</v>
+        <v>344042833.2097635</v>
       </c>
       <c r="L16">
-        <v>963731592.8368154</v>
+        <v>4185065911.492253</v>
       </c>
       <c r="M16">
-        <v>562520527.0919441</v>
+        <v>2321280247.712681</v>
       </c>
       <c r="N16">
-        <v>1377635135.395226</v>
+        <v>6210060715.804034</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>41594.12233561477</v>
+        <v>384989.1662475551</v>
       </c>
       <c r="D17">
-        <v>29545.51206382153</v>
+        <v>276422.0106009928</v>
       </c>
       <c r="E17">
-        <v>51364.74233097701</v>
+        <v>492697.3526181864</v>
       </c>
       <c r="F17">
-        <v>122137.8781134041</v>
+        <v>1119403.991155143</v>
       </c>
       <c r="G17">
-        <v>53668.38116603896</v>
+        <v>489260.930662933</v>
       </c>
       <c r="H17">
-        <v>230476.4186145855</v>
+        <v>2206808.921707753</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>16244337789.08275</v>
+        <v>148880730823.634</v>
       </c>
       <c r="M17">
-        <v>7137894695.083182</v>
+        <v>65071703778.17009</v>
       </c>
       <c r="N17">
-        <v>30653363675.73988</v>
+        <v>293505586587.1311</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>30664.03333429497</v>
+        <v>299102.6479928473</v>
       </c>
       <c r="D18">
-        <v>21781.55267933359</v>
+        <v>232189.9361119196</v>
       </c>
       <c r="E18">
-        <v>37867.13320540302</v>
+        <v>367001.6792238866</v>
       </c>
       <c r="F18">
-        <v>89881.34818002082</v>
+        <v>864682.1518575784</v>
       </c>
       <c r="G18">
-        <v>39494.59846816665</v>
+        <v>406391.3249949201</v>
       </c>
       <c r="H18">
-        <v>169607.7543573139</v>
+        <v>1641062.240329425</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>11954219307.94277</v>
+        <v>115002726197.0579</v>
       </c>
       <c r="M18">
-        <v>5252781596.266165</v>
+        <v>54050046224.32437</v>
       </c>
       <c r="N18">
-        <v>22557831329.52275</v>
+        <v>218261277963.8136</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>64101.02771560722</v>
+        <v>542460.2195339629</v>
       </c>
       <c r="D19">
-        <v>45802.08742320828</v>
+        <v>351263.6144924493</v>
       </c>
       <c r="E19">
-        <v>79077.29581720218</v>
+        <v>727299.4190330927</v>
       </c>
       <c r="F19">
-        <v>202792.6162261039</v>
+        <v>1694501.330409928</v>
       </c>
       <c r="G19">
-        <v>89750.98252888114</v>
+        <v>667473.8853996802</v>
       </c>
       <c r="H19">
-        <v>382194.3147598401</v>
+        <v>3495414.942015618</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>26971417958.07182</v>
+        <v>225368676944.5204</v>
       </c>
       <c r="M19">
-        <v>11936880676.34119</v>
+        <v>88774026758.15747</v>
       </c>
       <c r="N19">
-        <v>50831843863.05874</v>
+        <v>464890187288.0771</v>
       </c>
     </row>
   </sheetData>
